--- a/dev_test/Diversification/Self Created Dataset/Manual Created Diversified Dataset/Disturbed Diversifications/Clinic_Visits/Clinic_Visits_original_2.xlsx
+++ b/dev_test/Diversification/Self Created Dataset/Manual Created Diversified Dataset/Disturbed Diversifications/Clinic_Visits/Clinic_Visits_original_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repo\table-diversification\dev_test\Diversification\Self Created Dataset\Manual Created Diversified Dataset\Disturbed Diversifications\Clinic_Visits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991757A5-C03A-400C-901D-7AF0A543C7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2BF57C-FACB-4587-B1F0-B94B8F7756F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Visits" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="75">
   <si>
     <t>VisitID</t>
   </si>
@@ -34,12 +34,6 @@
     <t>Age</t>
   </si>
   <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>Condition</t>
-  </si>
-  <si>
     <t>BP_Systolic</t>
   </si>
   <si>
@@ -70,6 +64,9 @@
     <t>P-1230</t>
   </si>
   <si>
+    <t>F</t>
+  </si>
+  <si>
     <t>Hypertension</t>
   </si>
   <si>
@@ -94,6 +91,9 @@
     <t>P-1214</t>
   </si>
   <si>
+    <t>M</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
@@ -244,10 +244,7 @@
     <t>P-1228</t>
   </si>
   <si>
-    <t>Fale</t>
-  </si>
-  <si>
-    <t>Male</t>
+    <t>Gender, Condition</t>
   </si>
 </sst>
 </file>
@@ -276,7 +273,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -299,13 +296,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -611,9 +640,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -626,52 +655,50 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
       </c>
       <c r="D2">
         <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>136</v>
@@ -680,39 +707,39 @@
         <v>86</v>
       </c>
       <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
         <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
       </c>
       <c r="K2">
         <v>500</v>
       </c>
       <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
         <v>19</v>
       </c>
-      <c r="M2" t="s">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
       </c>
       <c r="D3">
         <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>128</v>
@@ -721,22 +748,22 @@
         <v>73</v>
       </c>
       <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
         <v>17</v>
-      </c>
-      <c r="J3" t="s">
-        <v>18</v>
       </c>
       <c r="K3">
         <v>600</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -750,10 +777,10 @@
         <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>119</v>
@@ -762,22 +789,22 @@
         <v>96</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K4">
         <v>500</v>
       </c>
       <c r="L4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -791,7 +818,7 @@
         <v>62</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
         <v>31</v>
@@ -803,7 +830,7 @@
         <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
         <v>32</v>
@@ -812,13 +839,13 @@
         <v>700</v>
       </c>
       <c r="L5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -832,10 +859,10 @@
         <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>152</v>
@@ -844,7 +871,7 @@
         <v>96</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
         <v>37</v>
@@ -853,13 +880,13 @@
         <v>600</v>
       </c>
       <c r="L6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -873,7 +900,7 @@
         <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
         <v>40</v>
@@ -885,7 +912,7 @@
         <v>97</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
         <v>37</v>
@@ -894,13 +921,13 @@
         <v>400</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -914,10 +941,10 @@
         <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>110</v>
@@ -926,22 +953,22 @@
         <v>82</v>
       </c>
       <c r="I8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" t="s">
         <v>17</v>
-      </c>
-      <c r="J8" t="s">
-        <v>18</v>
       </c>
       <c r="K8">
         <v>500</v>
       </c>
       <c r="L8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -949,13 +976,13 @@
         <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
         <v>46</v>
@@ -967,7 +994,7 @@
         <v>74</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J9" t="s">
         <v>32</v>
@@ -976,13 +1003,13 @@
         <v>400</v>
       </c>
       <c r="L9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M9" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -996,7 +1023,7 @@
         <v>75</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
         <v>46</v>
@@ -1008,22 +1035,22 @@
         <v>88</v>
       </c>
       <c r="I10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" t="s">
         <v>17</v>
-      </c>
-      <c r="J10" t="s">
-        <v>18</v>
       </c>
       <c r="K10">
         <v>700</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -1037,7 +1064,7 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
@@ -1049,7 +1076,7 @@
         <v>94</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J11" t="s">
         <v>37</v>
@@ -1058,13 +1085,13 @@
         <v>400</v>
       </c>
       <c r="L11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -1078,7 +1105,7 @@
         <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
         <v>31</v>
@@ -1090,7 +1117,7 @@
         <v>86</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J12" t="s">
         <v>37</v>
@@ -1099,13 +1126,13 @@
         <v>500</v>
       </c>
       <c r="L12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M12" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>56</v>
       </c>
@@ -1119,7 +1146,7 @@
         <v>51</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="F13" t="s">
         <v>31</v>
@@ -1131,7 +1158,7 @@
         <v>91</v>
       </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J13" t="s">
         <v>32</v>
@@ -1140,13 +1167,13 @@
         <v>600</v>
       </c>
       <c r="L13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -1160,10 +1187,10 @@
         <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G14">
         <v>147</v>
@@ -1172,7 +1199,7 @@
         <v>67</v>
       </c>
       <c r="I14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J14" t="s">
         <v>37</v>
@@ -1181,13 +1208,13 @@
         <v>400</v>
       </c>
       <c r="L14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -1201,7 +1228,7 @@
         <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
@@ -1213,7 +1240,7 @@
         <v>84</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J15" t="s">
         <v>37</v>
@@ -1222,13 +1249,13 @@
         <v>700</v>
       </c>
       <c r="L15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>64</v>
       </c>
@@ -1236,13 +1263,13 @@
         <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D16">
         <v>56</v>
       </c>
       <c r="E16" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s">
         <v>46</v>
@@ -1254,7 +1281,7 @@
         <v>79</v>
       </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J16" t="s">
         <v>32</v>
@@ -1263,13 +1290,13 @@
         <v>700</v>
       </c>
       <c r="L16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" t="s">
         <v>19</v>
       </c>
-      <c r="M16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -1283,7 +1310,7 @@
         <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
         <v>67</v>
@@ -1295,7 +1322,7 @@
         <v>93</v>
       </c>
       <c r="I17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J17" t="s">
         <v>32</v>
@@ -1304,13 +1331,13 @@
         <v>500</v>
       </c>
       <c r="L17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M17" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -1324,10 +1351,10 @@
         <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18">
         <v>158</v>
@@ -1336,22 +1363,22 @@
         <v>80</v>
       </c>
       <c r="I18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K18">
         <v>600</v>
       </c>
       <c r="L18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>71</v>
       </c>
@@ -1365,7 +1392,7 @@
         <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
@@ -1377,7 +1404,7 @@
         <v>79</v>
       </c>
       <c r="I19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J19" t="s">
         <v>32</v>
@@ -1386,13 +1413,16 @@
         <v>500</v>
       </c>
       <c r="L19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M19" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
